--- a/graficos/NMF_mejores_porc.xlsx
+++ b/graficos/NMF_mejores_porc.xlsx
@@ -67,64 +67,64 @@
     <t>comisión_lim</t>
   </si>
   <si>
-    <t>denuncia_dom</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dom_K3_4</t>
+    <t>antecedentes_dom</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>comisión_lim_denuncia_dom_K3_3</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dom_K3_2</t>
-  </si>
-  <si>
-    <t>denuncia_dictamen_dom</t>
+    <t>comisión_lim_antecedentes_dom_K3_3</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dom_K3_2</t>
+  </si>
+  <si>
+    <t>comisión_lim_antecedentes_dom_K3_4</t>
+  </si>
+  <si>
+    <t>antecedentes_dictamen_dom</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_dictamen_dom_K3_8</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>todos_denuncia_dictamen_dom_K3_7</t>
+    <t>todos_antecedentes_dictamen_dom_K3_7</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>todos_denuncia_dictamen_dom_K3_5</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>todos_denuncia_dictamen_dom_K3_8</t>
+    <t>todos_antecedentes_dictamen_dom_K3_5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>comisión_lim_contenido_dom_K3_6</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_dictamen_dom_K3_2</t>
+  </si>
+  <si>
+    <t>comisión_lim_contenido_dom_K3_7</t>
   </si>
   <si>
     <t>comisión_lim_contenido_dom_K3_5</t>
   </si>
   <si>
-    <t>todos_denuncia_dictamen_dom_K3_2</t>
-  </si>
-  <si>
-    <t>todos_denuncia_dictamen_dom_K3_4</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>todos_antecedentes_dictamen_dom_K3_4</t>
   </si>
   <si>
     <t>todos_contenido_dom_K3_6</t>
   </si>
   <si>
-    <t>comisión_lim_contenido_dom_K3_6</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dom_K3_7</t>
-  </si>
-  <si>
-    <t>comisión_lim_contenido_dom_K3_7</t>
+    <t>comisión_lim_antecedentes_dom_K3_7</t>
   </si>
   <si>
     <t>comisión_lim_contenido_dom_K3_4</t>
@@ -133,16 +133,16 @@
     <t>comisión_lim_contenido_dom_K3_2</t>
   </si>
   <si>
+    <t>comisión_lim_contenido_dom_K3_8</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>comisión_lim_denuncia_dom_K3_1</t>
-  </si>
-  <si>
-    <t>comisión_lim_denuncia_dom_K3_6</t>
-  </si>
-  <si>
-    <t>comisión_lim_contenido_dom_K3_3</t>
+    <t>comisión_lim_antecedentes_dom_K3_1</t>
+  </si>
+  <si>
+    <t>todos_antecedentes_dictamen_dom_K3_3</t>
   </si>
 </sst>
 </file>
@@ -624,16 +624,16 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3">
         <v>0.7333333333333333</v>
       </c>
       <c r="G4" s="3">
-        <v>-0.8139623405267572</v>
+        <v>-0.8233544913184341</v>
       </c>
       <c r="H4" s="2">
         <v>9</v>
@@ -656,7 +656,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>20</v>
@@ -665,7 +665,7 @@
         <v>0.7333333333333333</v>
       </c>
       <c r="G5" s="3">
-        <v>-0.8233544913184341</v>
+        <v>-0.8139623405267572</v>
       </c>
       <c r="H5" s="2">
         <v>9</v>
@@ -688,7 +688,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>21</v>
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3">
-        <v>-0.4933203434608211</v>
+        <v>-0.5436726587039878</v>
       </c>
       <c r="H7" s="2">
         <v>10</v>
@@ -761,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="3">
-        <v>-0.4909224815776049</v>
+        <v>-0.4933203434608211</v>
       </c>
       <c r="H8" s="2">
         <v>10</v>
@@ -793,7 +793,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="3">
-        <v>-0.5436726587039878</v>
+        <v>-0.4909224815776049</v>
       </c>
       <c r="H9" s="2">
         <v>10</v>
@@ -816,16 +816,16 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3">
         <v>0.8</v>
       </c>
       <c r="G10" s="3">
-        <v>-0.4878392853046886</v>
+        <v>-0.4341738392906276</v>
       </c>
       <c r="H10" s="2">
         <v>9</v>
@@ -851,7 +851,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11" s="3">
         <v>0.8</v>
@@ -871,25 +871,25 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F12" s="3">
         <v>0.8</v>
       </c>
       <c r="G12" s="3">
-        <v>-0.6886350793340585</v>
+        <v>-0.4988824865641424</v>
       </c>
       <c r="H12" s="2">
         <v>9</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
@@ -912,7 +912,7 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>33</v>
@@ -921,7 +921,7 @@
         <v>0.8</v>
       </c>
       <c r="G13" s="3">
-        <v>-0.4837030503107201</v>
+        <v>-0.4878392853046886</v>
       </c>
       <c r="H13" s="2">
         <v>9</v>
@@ -935,16 +935,16 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>34</v>
@@ -953,7 +953,7 @@
         <v>0.8</v>
       </c>
       <c r="G14" s="3">
-        <v>-0.4341738392906276</v>
+        <v>-0.6886350793340585</v>
       </c>
       <c r="H14" s="2">
         <v>9</v>
@@ -967,16 +967,16 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>35</v>
@@ -985,7 +985,7 @@
         <v>0.8</v>
       </c>
       <c r="G15" s="3">
-        <v>-0.7009833112641539</v>
+        <v>-0.4837030503107201</v>
       </c>
       <c r="H15" s="2">
         <v>9</v>
@@ -1002,13 +1002,13 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>36</v>
@@ -1017,7 +1017,7 @@
         <v>0.8</v>
       </c>
       <c r="G16" s="3">
-        <v>-0.4988824865641424</v>
+        <v>-0.7009833112641539</v>
       </c>
       <c r="H16" s="2">
         <v>9</v>
@@ -1098,22 +1098,22 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="F19" s="3">
         <v>0.8666666666666667</v>
       </c>
       <c r="G19" s="3">
-        <v>-0.6079800856092291</v>
+        <v>-0.430918719483837</v>
       </c>
       <c r="H19" s="2">
         <v>9</v>
@@ -1136,7 +1136,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>41</v>
@@ -1145,7 +1145,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="G20" s="3">
-        <v>-1.246672238986651</v>
+        <v>-0.6079800856092291</v>
       </c>
       <c r="H20" s="2">
         <v>9</v>
@@ -1159,16 +1159,16 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>42</v>
@@ -1177,7 +1177,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="G21" s="3">
-        <v>-0.4673191029688195</v>
+        <v>-0.7475183682169816</v>
       </c>
       <c r="H21" s="2">
         <v>9</v>
